--- a/tcmb faiz/tcmb_faiz.xlsx
+++ b/tcmb faiz/tcmb_faiz.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1190"/>
+  <dimension ref="A1:G1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8176,7 +8176,9 @@
       <c r="C338" t="n">
         <v>8.77</v>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="n">
+        <v>10</v>
+      </c>
       <c r="E338" t="n">
         <v>434.3229</v>
       </c>
@@ -27468,7 +27470,9 @@
       <c r="C1178" t="n">
         <v>37</v>
       </c>
-      <c r="D1178" t="inlineStr"/>
+      <c r="D1178" t="n">
+        <v>36.86</v>
+      </c>
       <c r="E1178" t="n">
         <v>-855.06237</v>
       </c>
@@ -27581,7 +27585,9 @@
       <c r="C1183" t="n">
         <v>37</v>
       </c>
-      <c r="D1183" t="inlineStr"/>
+      <c r="D1183" t="n">
+        <v>36.91</v>
+      </c>
       <c r="E1183" t="n">
         <v>-1008.25257</v>
       </c>
@@ -27625,7 +27631,9 @@
       <c r="C1185" t="n">
         <v>37</v>
       </c>
-      <c r="D1185" t="inlineStr"/>
+      <c r="D1185" t="n">
+        <v>36.51</v>
+      </c>
       <c r="E1185" t="n">
         <v>-657.76378</v>
       </c>
@@ -27646,7 +27654,9 @@
       <c r="C1186" t="n">
         <v>37</v>
       </c>
-      <c r="D1186" t="inlineStr"/>
+      <c r="D1186" t="n">
+        <v>36.49</v>
+      </c>
       <c r="E1186" t="n">
         <v>-771.83547</v>
       </c>
@@ -27730,11 +27740,15 @@
       <c r="A1190" s="1" t="n">
         <v>46290</v>
       </c>
-      <c r="B1190" t="inlineStr"/>
+      <c r="B1190" t="n">
+        <v>36.8804</v>
+      </c>
       <c r="C1190" t="n">
         <v>37</v>
       </c>
-      <c r="D1190" t="inlineStr"/>
+      <c r="D1190" t="n">
+        <v>36.88</v>
+      </c>
       <c r="E1190" t="n">
         <v>-780.37487</v>
       </c>
@@ -27742,6 +27756,92 @@
         <v>48.7671</v>
       </c>
       <c r="G1190" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>36.8757</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>-863.7507900000001</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>48.7901</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>36.8688</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>-839.0989000000001</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>48.9008</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>36.9244</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1193" t="inlineStr"/>
+      <c r="E1193" t="n">
+        <v>-631.8851</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>48.9131</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1194" t="inlineStr"/>
+      <c r="C1194" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1194" t="inlineStr"/>
+      <c r="E1194" t="n">
+        <v>-579.0565300000001</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>48.9303</v>
+      </c>
+      <c r="G1194" t="n">
         <v>37</v>
       </c>
     </row>
@@ -30575,7 +30675,9 @@
       <c r="A141" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>37</v>
+      </c>
       <c r="C141" t="n">
         <v>23.69</v>
       </c>
@@ -30616,7 +30718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R247"/>
+  <dimension ref="A1:R248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40099,6 +40201,62 @@
       </c>
       <c r="R247" t="n">
         <v>269567.556</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B248" t="n">
+        <v>27508886135</v>
+      </c>
+      <c r="C248" t="n">
+        <v>6941595414</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3463548565</v>
+      </c>
+      <c r="E248" t="n">
+        <v>9579000375</v>
+      </c>
+      <c r="F248" t="n">
+        <v>8921871745</v>
+      </c>
+      <c r="G248" t="n">
+        <v>203995792</v>
+      </c>
+      <c r="H248" t="n">
+        <v>81015190</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1104434631</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1294503</v>
+      </c>
+      <c r="K248" t="n">
+        <v>3451825911</v>
+      </c>
+      <c r="L248" t="n">
+        <v>11722654</v>
+      </c>
+      <c r="M248" t="n">
+        <v>128786448</v>
+      </c>
+      <c r="N248" t="n">
+        <v>115668712</v>
+      </c>
+      <c r="O248" t="n">
+        <v>215349450</v>
+      </c>
+      <c r="P248" t="n">
+        <v>215873875</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>20877345765</v>
+      </c>
+      <c r="R248" t="n">
+        <v>269555.333</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb faiz/tcmb_faiz.xlsx
+++ b/tcmb faiz/tcmb_faiz.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1199"/>
+  <dimension ref="A1:G1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27943,7 +27943,9 @@
       <c r="A1199" s="1" t="n">
         <v>46303</v>
       </c>
-      <c r="B1199" t="inlineStr"/>
+      <c r="B1199" t="n">
+        <v>36.8477</v>
+      </c>
       <c r="C1199" t="n">
         <v>37</v>
       </c>
@@ -27957,6 +27959,27 @@
         <v>49.1091</v>
       </c>
       <c r="G1199" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1200" t="inlineStr"/>
+      <c r="C1200" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>-672.5098</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>49.1267</v>
+      </c>
+      <c r="G1200" t="n">
         <v>37</v>
       </c>
     </row>

--- a/tcmb faiz/tcmb_faiz.xlsx
+++ b/tcmb faiz/tcmb_faiz.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1200"/>
+  <dimension ref="A1:G1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27966,7 +27966,9 @@
       <c r="A1200" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B1200" t="inlineStr"/>
+      <c r="B1200" t="n">
+        <v>36.9235</v>
+      </c>
       <c r="C1200" t="n">
         <v>37</v>
       </c>
@@ -27980,6 +27982,94 @@
         <v>49.1267</v>
       </c>
       <c r="G1200" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>36.8915</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>-751.3056700000001</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>49.1274</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>36.8411</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>-1098.73123</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>49.2471</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>36.7693</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>-1029.41045</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>49.2794</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1204" t="inlineStr"/>
+      <c r="C1204" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1204" t="inlineStr"/>
+      <c r="E1204" t="n">
+        <v>-1042.16608</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>49.3041</v>
+      </c>
+      <c r="G1204" t="n">
         <v>37</v>
       </c>
     </row>
@@ -30858,7 +30948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R249"/>
+  <dimension ref="A1:R250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40393,7 +40483,7 @@
         <v>215873875</v>
       </c>
       <c r="Q248" t="n">
-        <v>20877345765</v>
+        <v>20877507869</v>
       </c>
       <c r="R248" t="n">
         <v>269555.333</v>
@@ -40449,10 +40539,66 @@
         <v>217142717</v>
       </c>
       <c r="Q249" t="n">
-        <v>20751303339</v>
+        <v>20750688985</v>
       </c>
       <c r="R249" t="n">
         <v>266710.332</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B250" t="n">
+        <v>27733548690</v>
+      </c>
+      <c r="C250" t="n">
+        <v>6976701795</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3471557486</v>
+      </c>
+      <c r="E250" t="n">
+        <v>9737823553</v>
+      </c>
+      <c r="F250" t="n">
+        <v>8948876050</v>
+      </c>
+      <c r="G250" t="n">
+        <v>202572999</v>
+      </c>
+      <c r="H250" t="n">
+        <v>80831610</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1118858359</v>
+      </c>
+      <c r="J250" t="n">
+        <v>947060</v>
+      </c>
+      <c r="K250" t="n">
+        <v>3461190373</v>
+      </c>
+      <c r="L250" t="n">
+        <v>10367113</v>
+      </c>
+      <c r="M250" t="n">
+        <v>125346072</v>
+      </c>
+      <c r="N250" t="n">
+        <v>117258866</v>
+      </c>
+      <c r="O250" t="n">
+        <v>207195477</v>
+      </c>
+      <c r="P250" t="n">
+        <v>217136849</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>20755622558</v>
+      </c>
+      <c r="R250" t="n">
+        <v>265799.185</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb faiz/tcmb_faiz.xlsx
+++ b/tcmb faiz/tcmb_faiz.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1205"/>
+  <dimension ref="A1:G1209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27815,7 +27815,9 @@
       <c r="C1193" t="n">
         <v>37</v>
       </c>
-      <c r="D1193" t="inlineStr"/>
+      <c r="D1193" t="n">
+        <v>36.92</v>
+      </c>
       <c r="E1193" t="n">
         <v>-631.8851</v>
       </c>
@@ -27836,7 +27838,9 @@
       <c r="C1194" t="n">
         <v>37</v>
       </c>
-      <c r="D1194" t="inlineStr"/>
+      <c r="D1194" t="n">
+        <v>36.82</v>
+      </c>
       <c r="E1194" t="n">
         <v>-579.0565300000001</v>
       </c>
@@ -28081,11 +28085,15 @@
       <c r="A1205" s="1" t="n">
         <v>46311</v>
       </c>
-      <c r="B1205" t="inlineStr"/>
+      <c r="B1205" t="n">
+        <v>36.7953</v>
+      </c>
       <c r="C1205" t="n">
         <v>37</v>
       </c>
-      <c r="D1205" t="inlineStr"/>
+      <c r="D1205" t="n">
+        <v>36.8</v>
+      </c>
       <c r="E1205" t="n">
         <v>-1112.95498</v>
       </c>
@@ -28093,6 +28101,92 @@
         <v>49.3315</v>
       </c>
       <c r="G1205" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>36.7703</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>-1206.59408</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>49.3573</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>36.8228</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>-1026.15365</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>49.4632</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>36.8509</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1208" t="inlineStr"/>
+      <c r="E1208" t="n">
+        <v>-1118.39443</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>49.4889</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1209" t="inlineStr"/>
+      <c r="C1209" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1209" t="inlineStr"/>
+      <c r="E1209" t="n">
+        <v>-1186.77039</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>49.5123</v>
+      </c>
+      <c r="G1209" t="n">
         <v>37</v>
       </c>
     </row>
@@ -30971,7 +31065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R250"/>
+  <dimension ref="A1:R251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40622,6 +40716,62 @@
       </c>
       <c r="R250" t="n">
         <v>265799.185</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B251" t="n">
+        <v>27778612986</v>
+      </c>
+      <c r="C251" t="n">
+        <v>6871478289</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3389971024</v>
+      </c>
+      <c r="E251" t="n">
+        <v>9818949914</v>
+      </c>
+      <c r="F251" t="n">
+        <v>9008525105</v>
+      </c>
+      <c r="G251" t="n">
+        <v>206413088</v>
+      </c>
+      <c r="H251" t="n">
+        <v>81991889</v>
+      </c>
+      <c r="I251" t="n">
+        <v>1115154467</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1141069</v>
+      </c>
+      <c r="K251" t="n">
+        <v>3379616869</v>
+      </c>
+      <c r="L251" t="n">
+        <v>10354155</v>
+      </c>
+      <c r="M251" t="n">
+        <v>132126922</v>
+      </c>
+      <c r="N251" t="n">
+        <v>122403807</v>
+      </c>
+      <c r="O251" t="n">
+        <v>203559543</v>
+      </c>
+      <c r="P251" t="n">
+        <v>216868893</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>21313519484</v>
+      </c>
+      <c r="R251" t="n">
+        <v>266131.523</v>
       </c>
     </row>
   </sheetData>

--- a/tcmb faiz/tcmb_faiz.xlsx
+++ b/tcmb faiz/tcmb_faiz.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1213"/>
+  <dimension ref="A1:G1214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28281,6 +28281,27 @@
         <v>49.6997</v>
       </c>
       <c r="G1213" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1214" t="inlineStr"/>
+      <c r="C1214" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>-298.45402</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>49.6997</v>
+      </c>
+      <c r="G1214" t="n">
         <v>37</v>
       </c>
     </row>
